--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,75 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -734,8 +734,11 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,8 +787,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +840,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +893,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +916,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,8 +967,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,34 +1020,37 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1054,8 +1073,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1092,8 +1114,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1126,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,46 +1146,47 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>-400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
       <c r="L17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17" s="3">
         <v>100</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
@@ -1171,8 +1197,11 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,37 +1209,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1221,8 +1250,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1273,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,7 +1289,7 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1265,23 +1298,23 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
       </c>
       <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,8 +1324,11 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1300,37 +1336,37 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
+      <c r="O21" s="3">
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
@@ -1341,8 +1377,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,46 +1430,49 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1441,8 +1483,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1452,23 +1497,23 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1491,8 +1536,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,46 +1589,49 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1591,46 +1642,49 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1641,8 +1695,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1748,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1801,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1854,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1907,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1856,7 +1925,7 @@
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1865,23 +1934,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>100</v>
       </c>
       <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1891,46 +1960,49 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -1941,8 +2013,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,46 +2066,49 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -2041,52 +2119,55 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2177,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2200,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,46 +2221,47 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>900</v>
+      </c>
+      <c r="E41" s="3">
         <v>3200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3900</v>
-      </c>
-      <c r="G41" s="3">
-        <v>600</v>
       </c>
       <c r="H41" s="3">
         <v>600</v>
       </c>
       <c r="I41" s="3">
+        <v>600</v>
+      </c>
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
-      </c>
-      <c r="M41" s="3">
-        <v>1600</v>
       </c>
       <c r="N41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3">
+        <v>1600</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
@@ -2186,37 +2272,40 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E42" s="3">
         <v>7100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16200</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2227,8 +2316,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2236,8 +2325,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2274,8 +2366,8 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2286,8 +2378,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,8 +2431,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2345,23 +2443,23 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
@@ -2374,8 +2472,8 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2386,46 +2484,49 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E46" s="3">
         <v>10500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
-      </c>
-      <c r="M46" s="3">
-        <v>1600</v>
       </c>
       <c r="N46" s="3">
         <v>1600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>1600</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
@@ -2436,8 +2537,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2457,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
@@ -2466,17 +2570,17 @@
         <v>100</v>
       </c>
       <c r="L47" s="3">
+        <v>100</v>
+      </c>
+      <c r="M47" s="3">
         <v>200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,8 +2590,11 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2495,37 +2602,37 @@
         <v>2300</v>
       </c>
       <c r="E48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>800</v>
       </c>
       <c r="N48" s="3">
         <v>800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>800</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2536,8 +2643,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2696,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2749,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,8 +2802,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2703,11 +2822,11 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2724,8 +2843,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2736,8 +2855,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,47 +2908,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1900</v>
-      </c>
-      <c r="L54" s="3">
-        <v>2600</v>
       </c>
       <c r="M54" s="3">
         <v>2600</v>
       </c>
       <c r="N54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O54" s="3">
         <v>2700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +2961,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2984,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,37 +3005,38 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
       </c>
       <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -2914,8 +3044,8 @@
       <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>100</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -2926,8 +3056,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2976,8 +3109,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2990,18 +3126,18 @@
       <c r="F59" s="3">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3017,8 +3153,8 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -3026,37 +3162,40 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
       </c>
       <c r="F60" s="3">
+        <v>100</v>
+      </c>
+      <c r="G60" s="3">
         <v>200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>400</v>
       </c>
       <c r="I60" s="3">
         <v>400</v>
       </c>
       <c r="J60" s="3">
+        <v>400</v>
+      </c>
+      <c r="K60" s="3">
         <v>100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" s="3">
         <v>100</v>
@@ -3064,8 +3203,8 @@
       <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>100</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
@@ -3076,8 +3215,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3126,8 +3268,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3176,8 +3321,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3374,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3427,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,37 +3480,40 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
       </c>
       <c r="F66" s="3">
+        <v>100</v>
+      </c>
+      <c r="G66" s="3">
         <v>200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>400</v>
       </c>
       <c r="I66" s="3">
         <v>400</v>
       </c>
       <c r="J66" s="3">
+        <v>400</v>
+      </c>
+      <c r="K66" s="3">
         <v>100</v>
       </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
       <c r="L66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M66" s="3">
         <v>100</v>
@@ -3364,8 +3521,8 @@
       <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
+      <c r="O66" s="3">
+        <v>100</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
@@ -3376,8 +3533,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3556,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3607,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3660,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3713,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,46 +3766,49 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-100</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3646,8 +3819,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3872,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3925,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,47 +3978,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E76" s="3">
         <v>12700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4031,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,52 +4084,55 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3951,46 +4142,49 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -4001,8 +4195,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4218,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4059,8 +4257,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4071,8 +4269,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4322,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4375,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4428,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4481,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,46 +4534,49 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M89" s="3">
         <v>-100</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
@@ -4371,8 +4587,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,47 +4610,48 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4441,8 +4661,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4714,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,47 +4767,50 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4820,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4843,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4894,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4947,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5000,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,8 +5053,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4825,20 +5070,20 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>13900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4861,8 +5106,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4887,8 +5135,8 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4896,8 +5144,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4911,47 +5159,50 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,6 +5210,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,8 +738,11 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -790,8 +794,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -843,8 +850,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -896,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +930,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,37 +1040,40 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1076,8 +1096,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1117,8 +1140,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1129,8 +1152,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,49 +1173,50 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
       <c r="M17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3">
         <v>100</v>
       </c>
       <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1200,8 +1227,11 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1209,40 +1239,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
       <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1253,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,8 +1307,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1292,7 +1326,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1301,23 +1335,23 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1327,8 +1361,11 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1336,40 +1373,40 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
+      <c r="P21" s="3">
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
@@ -1380,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1433,49 +1473,52 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1486,8 +1529,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1500,23 +1546,23 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1539,8 +1585,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,49 +1641,52 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1645,49 +1697,52 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1698,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,8 +1977,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1928,7 +1998,7 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -1937,23 +2007,23 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1963,49 +2033,52 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -2016,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,49 +2145,52 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2122,55 +2201,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,49 +2308,50 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>600</v>
       </c>
       <c r="I41" s="3">
         <v>600</v>
       </c>
       <c r="J41" s="3">
+        <v>600</v>
+      </c>
+      <c r="K41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1200</v>
-      </c>
-      <c r="N41" s="3">
-        <v>1600</v>
       </c>
       <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3">
+        <v>1600</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
@@ -2275,40 +2362,43 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2409,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2328,8 +2418,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2369,8 +2462,8 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -2381,8 +2474,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2434,35 +2530,38 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2475,8 +2574,8 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2487,49 +2586,52 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E46" s="3">
         <v>9700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>1600</v>
       </c>
       <c r="O46" s="3">
         <v>1600</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
+      <c r="P46" s="3">
+        <v>1600</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
@@ -2540,8 +2642,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2564,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -2573,17 +2678,17 @@
         <v>100</v>
       </c>
       <c r="M47" s="3">
+        <v>100</v>
+      </c>
+      <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,49 +2698,52 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="E48" s="3">
         <v>2300</v>
       </c>
       <c r="F48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>800</v>
       </c>
       <c r="O48" s="3">
         <v>800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>800</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2646,8 +2754,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2699,8 +2810,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,8 +2922,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2825,11 +2945,11 @@
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2846,8 +2966,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2858,8 +2978,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,50 +3034,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E54" s="3">
         <v>12000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1900</v>
-      </c>
-      <c r="M54" s="3">
-        <v>2600</v>
       </c>
       <c r="N54" s="3">
         <v>2600</v>
       </c>
       <c r="O54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P54" s="3">
         <v>2700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,8 +3136,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3015,31 +3146,31 @@
         <v>600</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -3047,8 +3178,8 @@
       <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3">
+        <v>100</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3059,8 +3190,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3112,8 +3246,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3129,18 +3266,18 @@
       <c r="G59" s="3">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,8 +3293,8 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -3165,8 +3302,11 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3174,31 +3314,31 @@
         <v>700</v>
       </c>
       <c r="E60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
       </c>
       <c r="G60" s="3">
+        <v>100</v>
+      </c>
+      <c r="H60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>400</v>
       </c>
       <c r="J60" s="3">
         <v>400</v>
       </c>
       <c r="K60" s="3">
+        <v>400</v>
+      </c>
+      <c r="L60" s="3">
         <v>100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" s="3">
         <v>100</v>
@@ -3206,8 +3346,8 @@
       <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
+      <c r="P60" s="3">
+        <v>100</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
@@ -3218,8 +3358,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3271,8 +3414,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3324,8 +3470,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,8 +3638,11 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3492,31 +3650,31 @@
         <v>700</v>
       </c>
       <c r="E66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F66" s="3">
         <v>100</v>
       </c>
       <c r="G66" s="3">
+        <v>100</v>
+      </c>
+      <c r="H66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>400</v>
       </c>
       <c r="J66" s="3">
         <v>400</v>
       </c>
       <c r="K66" s="3">
+        <v>400</v>
+      </c>
+      <c r="L66" s="3">
         <v>100</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
       <c r="M66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N66" s="3">
         <v>100</v>
@@ -3524,8 +3682,8 @@
       <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
+      <c r="P66" s="3">
+        <v>100</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
@@ -3536,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,49 +3940,52 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -3822,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,50 +4164,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,55 +4276,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,49 +4337,52 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4198,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,8 +4417,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4260,8 +4459,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4272,8 +4471,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,8 +4751,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4546,40 +4763,40 @@
         <v>-400</v>
       </c>
       <c r="E89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -4590,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,50 +4831,51 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4885,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,50 +4997,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12500</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4897,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,8 +5299,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5073,20 +5319,20 @@
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>13900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -5109,8 +5355,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5138,8 +5387,8 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -5147,8 +5396,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5162,50 +5411,53 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5213,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,8 +742,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +944,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,40 +1060,43 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1143,8 +1166,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,52 +1200,53 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
         <v>900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3">
         <v>100</v>
       </c>
       <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
@@ -1230,8 +1257,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,43 +1269,43 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
       </c>
       <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1329,7 +1363,7 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1338,23 +1372,23 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1364,8 +1398,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1373,43 +1410,43 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,52 +1516,55 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
@@ -1532,13 +1575,16 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1549,23 +1595,23 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,52 +1693,55 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
@@ -1700,52 +1752,55 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2001,7 +2071,7 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2010,23 +2080,23 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,52 +2106,55 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,52 +2224,55 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
@@ -2204,58 +2283,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,52 +2395,53 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>600</v>
       </c>
       <c r="J41" s="3">
         <v>600</v>
       </c>
       <c r="K41" s="3">
+        <v>600</v>
+      </c>
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1600</v>
       </c>
       <c r="P41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3">
+        <v>1600</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
@@ -2365,43 +2452,46 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E42" s="3">
         <v>6600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
@@ -2412,8 +2502,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2421,8 +2511,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2465,8 +2558,8 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,38 +2629,41 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2577,8 +2676,8 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2589,52 +2688,55 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E46" s="3">
         <v>8600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1300</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1600</v>
       </c>
       <c r="P46" s="3">
         <v>1600</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
+      <c r="Q46" s="3">
+        <v>1600</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2672,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L47" s="3">
         <v>100</v>
@@ -2681,17 +2786,17 @@
         <v>100</v>
       </c>
       <c r="N47" s="3">
+        <v>100</v>
+      </c>
+      <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,52 +2806,55 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2300</v>
       </c>
       <c r="F48" s="3">
         <v>2300</v>
       </c>
       <c r="G48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
-      </c>
-      <c r="O48" s="3">
-        <v>800</v>
       </c>
       <c r="P48" s="3">
         <v>800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>800</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2948,11 +3068,11 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2969,8 +3089,8 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,53 +3160,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E54" s="3">
         <v>11600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1900</v>
-      </c>
-      <c r="N54" s="3">
-        <v>2600</v>
       </c>
       <c r="O54" s="3">
         <v>2600</v>
       </c>
       <c r="P54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q54" s="3">
         <v>2700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,43 +3267,44 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>600</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -3181,8 +3312,8 @@
       <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>100</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3249,8 +3383,11 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3269,18 +3406,18 @@
       <c r="H59" s="3">
         <v>0</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3296,8 +3433,8 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -3305,43 +3442,46 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E60" s="3">
         <v>700</v>
       </c>
       <c r="F60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="G60" s="3">
         <v>100</v>
       </c>
       <c r="H60" s="3">
+        <v>100</v>
+      </c>
+      <c r="I60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>400</v>
       </c>
       <c r="K60" s="3">
         <v>400</v>
       </c>
       <c r="L60" s="3">
+        <v>400</v>
+      </c>
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O60" s="3">
         <v>100</v>
@@ -3349,8 +3489,8 @@
       <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3">
+        <v>100</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
@@ -3361,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3417,8 +3560,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,43 +3796,46 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E66" s="3">
         <v>700</v>
       </c>
       <c r="F66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="G66" s="3">
         <v>100</v>
       </c>
       <c r="H66" s="3">
+        <v>100</v>
+      </c>
+      <c r="I66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>400</v>
       </c>
       <c r="K66" s="3">
         <v>400</v>
       </c>
       <c r="L66" s="3">
+        <v>400</v>
+      </c>
+      <c r="M66" s="3">
         <v>100</v>
       </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
       <c r="N66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O66" s="3">
         <v>100</v>
@@ -3685,8 +3843,8 @@
       <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
+      <c r="Q66" s="3">
+        <v>100</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,52 +4114,55 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-100</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,53 +4350,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E76" s="3">
         <v>11000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,58 +4468,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,52 +4532,55 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4462,8 +4661,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,52 +4968,55 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
         <v>-400</v>
       </c>
       <c r="F89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
         <v>-100</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,53 +5052,54 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,53 +5227,56 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12500</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,8 +5545,11 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5322,20 +5568,20 @@
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>13900</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5390,8 +5639,8 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -5399,8 +5648,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5414,53 +5663,56 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,86 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,31 +746,34 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -804,8 +808,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +870,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,8 +958,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,43 +1080,46 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1137,13 +1160,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1169,8 +1192,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,55 +1227,56 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>500</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
-        <v>900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1800</v>
-      </c>
       <c r="G17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>600</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3">
         <v>100</v>
       </c>
       <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
@@ -1260,55 +1287,58 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-500</v>
       </c>
       <c r="E18" s="3">
-        <v>-900</v>
+        <v>-500</v>
       </c>
       <c r="F18" s="3">
-        <v>-1800</v>
+        <v>-700</v>
       </c>
       <c r="G18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3">
         <v>-100</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
@@ -1319,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,16 +1375,17 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1366,7 +1400,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1375,23 +1409,23 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>-100</v>
       </c>
       <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1401,55 +1435,58 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-1000</v>
       </c>
       <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-300</v>
-      </c>
       <c r="H21" s="3">
-        <v>-1500</v>
+        <v>-400</v>
       </c>
       <c r="I21" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="J21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
+      <c r="R21" s="3">
+        <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
@@ -1460,31 +1497,34 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1519,55 +1559,58 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
@@ -1578,16 +1621,19 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1595,26 +1641,26 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,55 +1745,58 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
@@ -1755,55 +1807,58 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
@@ -1814,8 +1869,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,16 +2117,19 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -2074,7 +2144,7 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2083,23 +2153,23 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>100</v>
       </c>
       <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2109,55 +2179,58 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
@@ -2168,8 +2241,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,55 +2303,58 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
@@ -2286,61 +2365,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2350,8 +2432,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,55 +2482,56 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>600</v>
       </c>
       <c r="K41" s="3">
         <v>600</v>
       </c>
       <c r="L41" s="3">
+        <v>600</v>
+      </c>
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
-      </c>
-      <c r="P41" s="3">
-        <v>1600</v>
       </c>
       <c r="Q41" s="3">
         <v>1600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+      <c r="R41" s="3">
+        <v>1600</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
@@ -2455,46 +2542,49 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E42" s="3">
         <v>5900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2505,8 +2595,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2514,8 +2604,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2561,8 +2654,8 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2573,31 +2666,34 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2632,41 +2728,44 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2679,8 +2778,8 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2691,55 +2790,58 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1300</v>
-      </c>
-      <c r="P46" s="3">
-        <v>1600</v>
       </c>
       <c r="Q46" s="3">
         <v>1600</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+      <c r="R46" s="3">
+        <v>1600</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
@@ -2750,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2780,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3">
         <v>100</v>
@@ -2789,17 +2894,17 @@
         <v>100</v>
       </c>
       <c r="O47" s="3">
+        <v>100</v>
+      </c>
+      <c r="P47" s="3">
         <v>200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2809,55 +2914,58 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2300</v>
       </c>
       <c r="G48" s="3">
         <v>2300</v>
       </c>
       <c r="H48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>800</v>
       </c>
       <c r="Q48" s="3">
         <v>800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>800</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -2868,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3071,11 +3191,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -3092,8 +3212,8 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,56 +3286,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1900</v>
-      </c>
-      <c r="O54" s="3">
-        <v>2600</v>
       </c>
       <c r="P54" s="3">
         <v>2600</v>
       </c>
       <c r="Q54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R54" s="3">
         <v>2700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,8 +3398,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3277,37 +3408,37 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>600</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -3315,8 +3446,8 @@
       <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>100</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3327,8 +3458,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3386,41 +3520,44 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3436,8 +3573,8 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -3445,8 +3582,11 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3454,37 +3594,37 @@
         <v>100</v>
       </c>
       <c r="E60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F60" s="3">
         <v>700</v>
       </c>
       <c r="G60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H60" s="3">
         <v>100</v>
       </c>
       <c r="I60" s="3">
+        <v>100</v>
+      </c>
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>400</v>
       </c>
       <c r="L60" s="3">
         <v>400</v>
       </c>
       <c r="M60" s="3">
+        <v>400</v>
+      </c>
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
       <c r="O60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P60" s="3">
         <v>100</v>
@@ -3492,8 +3632,8 @@
       <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+      <c r="R60" s="3">
+        <v>100</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
@@ -3504,8 +3644,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3563,31 +3706,34 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,8 +3954,11 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3808,37 +3966,37 @@
         <v>100</v>
       </c>
       <c r="E66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F66" s="3">
         <v>700</v>
       </c>
       <c r="G66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H66" s="3">
         <v>100</v>
       </c>
       <c r="I66" s="3">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3">
         <v>200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100</v>
-      </c>
-      <c r="K66" s="3">
-        <v>400</v>
       </c>
       <c r="L66" s="3">
         <v>400</v>
       </c>
       <c r="M66" s="3">
+        <v>400</v>
+      </c>
+      <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
       <c r="O66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P66" s="3">
         <v>100</v>
@@ -3846,8 +4004,8 @@
       <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
+      <c r="R66" s="3">
+        <v>100</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,55 +4288,58 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-5400</v>
+        <v>-9400</v>
       </c>
       <c r="E72" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="I72" s="3">
         <v>-5000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-1400</v>
-      </c>
       <c r="J72" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,56 +4536,59 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E76" s="3">
         <v>10600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,61 +4660,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4535,55 +4727,58 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
@@ -4594,8 +4789,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +4815,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4664,8 +4863,8 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,55 +5185,58 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-400</v>
       </c>
       <c r="F89" s="3">
         <v>-400</v>
       </c>
       <c r="G89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,56 +5273,57 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,56 +5457,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,31 +5545,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,8 +5791,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5571,20 +5817,20 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>13900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -5607,8 +5853,11 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5642,8 +5891,8 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -5651,8 +5900,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5666,8 +5915,11 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5675,47 +5927,47 @@
         <v>-700</v>
       </c>
       <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +5975,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,90 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,8 +749,11 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,8 +778,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -811,8 +814,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +879,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +971,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1099,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1109,20 +1128,20 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1145,8 +1164,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1160,17 +1182,17 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1195,8 +1217,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1207,8 +1229,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,8 +1253,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1240,46 +1266,46 @@
         <v>500</v>
       </c>
       <c r="F17" s="3">
+        <v>500</v>
+      </c>
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="3">
         <v>100</v>
       </c>
       <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1290,8 +1316,11 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1302,46 +1331,46 @@
         <v>-500</v>
       </c>
       <c r="F18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="3">
         <v>-100</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
@@ -1352,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,19 +1408,20 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
@@ -1403,7 +1436,7 @@
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1412,23 +1445,23 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>-100</v>
       </c>
       <c r="R20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,58 +1471,61 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-400</v>
       </c>
       <c r="I21" s="3">
         <v>-400</v>
       </c>
       <c r="J21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
+      <c r="S21" s="3">
+        <v>0</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
@@ -1500,8 +1536,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1526,8 +1565,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1562,58 +1601,61 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1624,46 +1666,49 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1686,8 +1731,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,58 +1796,61 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1810,58 +1861,61 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,19 +2186,22 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
@@ -2147,7 +2216,7 @@
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2156,23 +2225,23 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>100</v>
       </c>
       <c r="R32" s="3">
+        <v>100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,58 +2251,61 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,58 +2381,61 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2368,64 +2446,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,58 +2568,59 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3900</v>
-      </c>
-      <c r="K41" s="3">
-        <v>600</v>
       </c>
       <c r="L41" s="3">
         <v>600</v>
       </c>
       <c r="M41" s="3">
+        <v>600</v>
+      </c>
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>1600</v>
       </c>
       <c r="R41" s="3">
         <v>1600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>1600</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2545,49 +2631,52 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E42" s="3">
         <v>5200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2598,8 +2687,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2607,8 +2696,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2657,8 +2749,8 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -2669,8 +2761,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2695,8 +2790,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2731,8 +2826,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2757,18 +2855,18 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
@@ -2781,8 +2879,8 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2793,58 +2891,61 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E46" s="3">
         <v>6200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>1600</v>
       </c>
       <c r="R46" s="3">
         <v>1600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>1600</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2855,8 +2956,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2888,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>100</v>
@@ -2897,17 +3001,17 @@
         <v>100</v>
       </c>
       <c r="P47" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q47" s="3">
         <v>200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,58 +3021,61 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2300</v>
       </c>
       <c r="H48" s="3">
         <v>2300</v>
       </c>
       <c r="I48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>800</v>
       </c>
       <c r="R48" s="3">
         <v>800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>800</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -2979,8 +3086,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3281,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3194,11 +3313,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -3215,8 +3334,8 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3227,8 +3346,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,59 +3411,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1900</v>
-      </c>
-      <c r="P54" s="3">
-        <v>2600</v>
       </c>
       <c r="Q54" s="3">
         <v>2600</v>
       </c>
       <c r="R54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S54" s="3">
         <v>2700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,49 +3528,50 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>600</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -3449,8 +3579,8 @@
       <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>100</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3461,8 +3591,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3523,8 +3656,11 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3552,15 +3688,15 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3576,8 +3712,8 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -3585,49 +3721,52 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
       </c>
       <c r="F60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="G60" s="3">
         <v>700</v>
       </c>
       <c r="H60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I60" s="3">
         <v>100</v>
       </c>
       <c r="J60" s="3">
+        <v>100</v>
+      </c>
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>400</v>
       </c>
       <c r="M60" s="3">
         <v>400</v>
       </c>
       <c r="N60" s="3">
+        <v>400</v>
+      </c>
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="3">
         <v>100</v>
@@ -3635,8 +3774,8 @@
       <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>100</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3647,8 +3786,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3709,8 +3851,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3735,8 +3880,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3771,8 +3916,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,49 +4111,52 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
       </c>
       <c r="F66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="G66" s="3">
         <v>700</v>
       </c>
       <c r="H66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I66" s="3">
         <v>100</v>
       </c>
       <c r="J66" s="3">
+        <v>100</v>
+      </c>
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>400</v>
       </c>
       <c r="M66" s="3">
         <v>400</v>
       </c>
       <c r="N66" s="3">
+        <v>400</v>
+      </c>
+      <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3">
-        <v>0</v>
-      </c>
       <c r="P66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="3">
         <v>100</v>
@@ -4007,8 +4164,8 @@
       <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
+      <c r="S66" s="3">
+        <v>100</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
@@ -4019,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,58 +4461,61 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4353,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,59 +4721,62 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E76" s="3">
         <v>9800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +4851,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,58 +4921,61 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5013,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4866,8 +5064,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4878,8 +5076,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,58 +5401,61 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-400</v>
       </c>
       <c r="G89" s="3">
         <v>-400</v>
       </c>
       <c r="H89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
         <v>-100</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,59 +5493,60 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5336,8 +5556,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,59 +5686,62 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12500</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5751,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5572,8 +5805,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5608,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,8 +6036,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5820,20 +6065,20 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>13900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -5856,8 +6101,11 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5894,8 +6142,8 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5903,8 +6151,8 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -5918,59 +6166,62 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
         <v>-700</v>
       </c>
       <c r="F102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,8 +753,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -781,8 +785,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -817,8 +821,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +985,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,8 +1119,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1131,20 +1151,20 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1167,8 +1187,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1185,17 +1208,17 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1220,8 +1243,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,8 +1280,9 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1269,46 +1296,46 @@
         <v>500</v>
       </c>
       <c r="G17" s="3">
+        <v>500</v>
+      </c>
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R17" s="3">
         <v>100</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1319,8 +1346,11 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1334,46 +1364,46 @@
         <v>-500</v>
       </c>
       <c r="G18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3">
         <v>-100</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,22 +1442,23 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
@@ -1439,7 +1473,7 @@
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1448,23 +1482,23 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,61 +1508,64 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-400</v>
       </c>
       <c r="J21" s="3">
         <v>-400</v>
       </c>
       <c r="K21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
+      <c r="T21" s="3">
+        <v>0</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
@@ -1539,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1568,8 +1608,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1604,61 +1644,64 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1669,49 +1712,52 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,61 +1848,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1864,61 +1916,64 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,22 +2256,25 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
@@ -2219,7 +2289,7 @@
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2228,23 +2298,23 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,61 +2324,64 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,61 +2460,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,61 +2655,62 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3900</v>
-      </c>
-      <c r="L41" s="3">
-        <v>600</v>
       </c>
       <c r="M41" s="3">
         <v>600</v>
       </c>
       <c r="N41" s="3">
+        <v>600</v>
+      </c>
+      <c r="O41" s="3">
         <v>1900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1200</v>
-      </c>
-      <c r="R41" s="3">
-        <v>1600</v>
       </c>
       <c r="S41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>1600</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2634,52 +2721,55 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E42" s="3">
         <v>4900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2690,8 +2780,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2699,8 +2789,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2752,8 +2845,8 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -2764,8 +2857,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2793,8 +2889,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2829,8 +2925,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2858,18 +2957,18 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -2882,8 +2981,8 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -2894,61 +2993,64 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1300</v>
-      </c>
-      <c r="R46" s="3">
-        <v>1600</v>
       </c>
       <c r="S46" s="3">
         <v>1600</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>1600</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -2959,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2995,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>100</v>
@@ -3004,17 +3109,17 @@
         <v>100</v>
       </c>
       <c r="Q47" s="3">
+        <v>100</v>
+      </c>
+      <c r="R47" s="3">
         <v>200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,61 +3129,64 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2300</v>
       </c>
       <c r="I48" s="3">
         <v>2300</v>
       </c>
       <c r="J48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>800</v>
       </c>
       <c r="S48" s="3">
         <v>800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3">
+        <v>800</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3089,8 +3197,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3316,11 +3436,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -3337,8 +3457,8 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3537,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>2600</v>
       </c>
       <c r="R54" s="3">
         <v>2600</v>
       </c>
       <c r="S54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T54" s="3">
         <v>2700</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,52 +3659,53 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>600</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
@@ -3582,8 +3713,8 @@
       <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>100</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3594,8 +3725,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3659,8 +3793,11 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3691,15 +3828,15 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3715,8 +3852,8 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -3724,52 +3861,55 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100</v>
+      </c>
+      <c r="E60" s="3">
         <v>200</v>
-      </c>
-      <c r="E60" s="3">
-        <v>100</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
       </c>
       <c r="G60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="H60" s="3">
         <v>700</v>
       </c>
       <c r="I60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="J60" s="3">
         <v>100</v>
       </c>
       <c r="K60" s="3">
+        <v>100</v>
+      </c>
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>400</v>
       </c>
       <c r="N60" s="3">
         <v>400</v>
       </c>
       <c r="O60" s="3">
+        <v>400</v>
+      </c>
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
@@ -3777,8 +3917,8 @@
       <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>100</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3789,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3854,8 +3997,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3883,8 +4029,8 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,52 +4269,55 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100</v>
+      </c>
+      <c r="E66" s="3">
         <v>200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>100</v>
       </c>
       <c r="F66" s="3">
         <v>100</v>
       </c>
       <c r="G66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="H66" s="3">
         <v>700</v>
       </c>
       <c r="I66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="J66" s="3">
         <v>100</v>
       </c>
       <c r="K66" s="3">
+        <v>100</v>
+      </c>
+      <c r="L66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100</v>
-      </c>
-      <c r="M66" s="3">
-        <v>400</v>
       </c>
       <c r="N66" s="3">
         <v>400</v>
       </c>
       <c r="O66" s="3">
+        <v>400</v>
+      </c>
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3">
-        <v>0</v>
-      </c>
       <c r="Q66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R66" s="3">
         <v>100</v>
@@ -4167,8 +4325,8 @@
       <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
+      <c r="T66" s="3">
+        <v>100</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,61 +4635,64 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,62 +4907,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E76" s="3">
         <v>9300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,61 +5116,64 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5067,8 +5266,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,8 +5618,11 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5413,52 +5630,52 @@
         <v>-300</v>
       </c>
       <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-400</v>
       </c>
       <c r="H89" s="3">
         <v>-400</v>
       </c>
       <c r="I89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,8 +5714,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5503,53 +5724,53 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,62 +5916,65 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12500</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5808,8 +6042,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,8 +6282,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6068,20 +6314,20 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>13900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -6104,8 +6350,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6145,8 +6394,8 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -6154,8 +6403,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6169,62 +6418,65 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-700</v>
       </c>
       <c r="F102" s="3">
         <v>-700</v>
       </c>
       <c r="G102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H102" s="3">
         <v>1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,8 +757,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -788,8 +792,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -824,8 +828,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -892,8 +899,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,8 +999,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1139,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1154,20 +1174,20 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1190,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1211,17 +1234,17 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1246,8 +1269,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,13 +1307,14 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3">
         <v>500</v>
@@ -1299,46 +1326,46 @@
         <v>500</v>
       </c>
       <c r="H17" s="3">
+        <v>500</v>
+      </c>
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3">
         <v>100</v>
       </c>
       <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1349,13 +1376,16 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="E18" s="3">
         <v>-500</v>
@@ -1367,46 +1397,46 @@
         <v>-500</v>
       </c>
       <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>-100</v>
       </c>
       <c r="T18" s="3">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,25 +1476,26 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
@@ -1476,7 +1510,7 @@
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1485,23 +1519,23 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,64 +1545,67 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-400</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
       </c>
       <c r="L21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
+      <c r="U21" s="3">
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
@@ -1579,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1611,8 +1651,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1647,64 +1687,67 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1715,52 +1758,55 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,64 +1900,67 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1919,64 +1971,67 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,25 +2326,28 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
@@ -2292,7 +2362,7 @@
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2301,23 +2371,23 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,64 +2397,67 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,64 +2539,67 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2531,70 +2610,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,64 +2742,65 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3900</v>
-      </c>
-      <c r="M41" s="3">
-        <v>600</v>
       </c>
       <c r="N41" s="3">
         <v>600</v>
       </c>
       <c r="O41" s="3">
+        <v>600</v>
+      </c>
+      <c r="P41" s="3">
         <v>1900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
-      </c>
-      <c r="S41" s="3">
-        <v>1600</v>
       </c>
       <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>1600</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2724,55 +2811,58 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E42" s="3">
         <v>4200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
@@ -2783,8 +2873,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2792,8 +2882,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2848,8 +2941,8 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -2860,8 +2953,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2892,8 +2988,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2928,8 +3024,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2960,18 +3059,18 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -2984,8 +3083,8 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -2996,64 +3095,67 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1300</v>
-      </c>
-      <c r="S46" s="3">
-        <v>1600</v>
       </c>
       <c r="T46" s="3">
         <v>1600</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3">
+        <v>1600</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3103,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
         <v>100</v>
@@ -3112,17 +3217,17 @@
         <v>100</v>
       </c>
       <c r="R47" s="3">
+        <v>100</v>
+      </c>
+      <c r="S47" s="3">
         <v>200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3132,64 +3237,67 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2300</v>
       </c>
       <c r="J48" s="3">
         <v>2300</v>
       </c>
       <c r="K48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1100</v>
-      </c>
-      <c r="S48" s="3">
-        <v>800</v>
       </c>
       <c r="T48" s="3">
         <v>800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>800</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3200,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,8 +3521,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3439,11 +3559,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -3460,8 +3580,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,65 +3663,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E54" s="3">
         <v>9000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1900</v>
-      </c>
-      <c r="R54" s="3">
-        <v>2600</v>
       </c>
       <c r="S54" s="3">
         <v>2600</v>
       </c>
       <c r="T54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U54" s="3">
         <v>2700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,8 +3790,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3669,46 +3800,46 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>600</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -3716,8 +3847,8 @@
       <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>100</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3728,8 +3859,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3796,8 +3930,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3831,15 +3968,15 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3855,8 +3992,8 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -3864,8 +4001,11 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3873,46 +4013,46 @@
         <v>100</v>
       </c>
       <c r="E60" s="3">
+        <v>100</v>
+      </c>
+      <c r="F60" s="3">
         <v>200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>100</v>
       </c>
       <c r="G60" s="3">
         <v>100</v>
       </c>
       <c r="H60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="I60" s="3">
         <v>700</v>
       </c>
       <c r="J60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
-      </c>
-      <c r="N60" s="3">
-        <v>400</v>
       </c>
       <c r="O60" s="3">
         <v>400</v>
       </c>
       <c r="P60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
@@ -3920,8 +4060,8 @@
       <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>100</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -3932,8 +4072,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4000,8 +4143,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4032,8 +4178,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,8 +4427,11 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4281,46 +4439,46 @@
         <v>100</v>
       </c>
       <c r="E66" s="3">
+        <v>100</v>
+      </c>
+      <c r="F66" s="3">
         <v>200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>100</v>
       </c>
       <c r="G66" s="3">
         <v>100</v>
       </c>
       <c r="H66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="I66" s="3">
         <v>700</v>
       </c>
       <c r="J66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="K66" s="3">
         <v>100</v>
       </c>
       <c r="L66" s="3">
+        <v>100</v>
+      </c>
+      <c r="M66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100</v>
-      </c>
-      <c r="N66" s="3">
-        <v>400</v>
       </c>
       <c r="O66" s="3">
         <v>400</v>
       </c>
       <c r="P66" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
       <c r="R66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
@@ -4328,8 +4486,8 @@
       <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
+      <c r="U66" s="3">
+        <v>100</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,64 +4809,67 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,65 +5093,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5235,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,64 +5311,67 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5269,8 +5468,8 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,64 +5835,67 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E89" s="3">
         <v>-300</v>
       </c>
       <c r="F89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-400</v>
       </c>
       <c r="I89" s="3">
         <v>-400</v>
       </c>
       <c r="J89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S89" s="3">
         <v>-100</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,65 +5935,66 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,65 +6146,68 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>300</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6045,8 +6279,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,8 +6528,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6317,20 +6563,20 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>13900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -6353,8 +6599,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6397,8 +6646,8 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -6406,8 +6655,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6421,65 +6670,68 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-700</v>
       </c>
       <c r="G102" s="3">
         <v>-700</v>
       </c>
       <c r="H102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I102" s="3">
         <v>1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -764,8 +764,11 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -802,8 +805,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -838,8 +841,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,8 +918,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,8 +1026,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1088,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,8 +1178,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1200,20 +1219,20 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1236,8 +1255,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1263,17 +1285,17 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>1000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>1200</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1298,8 +1320,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
@@ -1310,8 +1332,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,8 +1360,9 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1347,7 +1373,7 @@
         <v>300</v>
       </c>
       <c r="F17" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G17" s="3">
         <v>500</v>
@@ -1359,46 +1385,46 @@
         <v>500</v>
       </c>
       <c r="J17" s="3">
+        <v>500</v>
+      </c>
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U17" s="3">
         <v>100</v>
       </c>
       <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1409,8 +1435,11 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1421,7 +1450,7 @@
         <v>-300</v>
       </c>
       <c r="F18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="3">
         <v>-500</v>
@@ -1433,46 +1462,46 @@
         <v>-500</v>
       </c>
       <c r="J18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3">
         <v>-100</v>
       </c>
       <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
@@ -1483,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,31 +1543,32 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1550,7 +1583,7 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1559,23 +1592,23 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
       </c>
       <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,70 +1618,73 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
         <v>-300</v>
       </c>
       <c r="F21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-400</v>
       </c>
       <c r="M21" s="3">
         <v>-400</v>
       </c>
       <c r="N21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-200</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
+      <c r="W21" s="3">
+        <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
@@ -1659,8 +1695,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1697,8 +1736,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1733,70 +1772,73 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E23" s="3">
         <v>-300</v>
       </c>
       <c r="F23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1807,58 +1849,61 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1881,8 +1926,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,70 +2003,73 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E26" s="3">
         <v>-300</v>
       </c>
       <c r="F26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -2029,70 +2080,73 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E27" s="3">
         <v>-300</v>
       </c>
       <c r="F27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2103,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,31 +2465,34 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2438,7 +2507,7 @@
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2447,23 +2516,23 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,70 +2542,73 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E33" s="3">
         <v>-300</v>
       </c>
       <c r="F33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2547,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,70 +2696,73 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E35" s="3">
         <v>-300</v>
       </c>
       <c r="F35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2695,76 +2773,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,70 +2915,71 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E41" s="3">
         <v>400</v>
       </c>
       <c r="F41" s="3">
+        <v>400</v>
+      </c>
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3900</v>
-      </c>
-      <c r="O41" s="3">
-        <v>600</v>
       </c>
       <c r="P41" s="3">
         <v>600</v>
       </c>
       <c r="Q41" s="3">
+        <v>600</v>
+      </c>
+      <c r="R41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1200</v>
-      </c>
-      <c r="U41" s="3">
-        <v>1600</v>
       </c>
       <c r="V41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="W41" s="3">
+        <v>1600</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2904,61 +2990,64 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E42" s="3">
         <v>3300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>16200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
@@ -2969,8 +3058,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -2978,8 +3067,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3040,8 +3132,8 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
@@ -3052,8 +3144,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3090,8 +3185,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3126,8 +3221,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3164,18 +3262,18 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -3188,8 +3286,8 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
@@ -3200,70 +3298,73 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1300</v>
-      </c>
-      <c r="U46" s="3">
-        <v>1600</v>
       </c>
       <c r="V46" s="3">
         <v>1600</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+      <c r="W46" s="3">
+        <v>1600</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
@@ -3274,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3319,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>100</v>
@@ -3328,17 +3432,17 @@
         <v>100</v>
       </c>
       <c r="T47" s="3">
+        <v>100</v>
+      </c>
+      <c r="U47" s="3">
         <v>200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,70 +3452,73 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2300</v>
       </c>
       <c r="L48" s="3">
         <v>2300</v>
       </c>
       <c r="M48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>800</v>
       </c>
       <c r="V48" s="3">
         <v>800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>800</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3422,8 +3529,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,8 +3760,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3685,11 +3804,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3706,8 +3825,8 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3718,8 +3837,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,71 +3914,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E54" s="3">
         <v>8900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1900</v>
-      </c>
-      <c r="T54" s="3">
-        <v>2600</v>
       </c>
       <c r="U54" s="3">
         <v>2600</v>
       </c>
       <c r="V54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="W54" s="3">
         <v>2700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,8 +4051,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3937,46 +4067,46 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
@@ -3984,8 +4114,8 @@
       <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>100</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -3996,8 +4126,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4070,8 +4203,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4111,15 +4247,15 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4135,8 +4271,8 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -4144,8 +4280,11 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4159,46 +4298,46 @@
         <v>100</v>
       </c>
       <c r="G60" s="3">
+        <v>100</v>
+      </c>
+      <c r="H60" s="3">
         <v>200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>100</v>
       </c>
       <c r="I60" s="3">
         <v>100</v>
       </c>
       <c r="J60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="K60" s="3">
         <v>700</v>
       </c>
       <c r="L60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="M60" s="3">
         <v>100</v>
       </c>
       <c r="N60" s="3">
+        <v>100</v>
+      </c>
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
-      </c>
-      <c r="P60" s="3">
-        <v>400</v>
       </c>
       <c r="Q60" s="3">
         <v>400</v>
       </c>
       <c r="R60" s="3">
+        <v>400</v>
+      </c>
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
       <c r="T60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
@@ -4206,8 +4345,8 @@
       <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
+      <c r="W60" s="3">
+        <v>100</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
@@ -4218,8 +4357,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4292,8 +4434,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4330,8 +4475,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4366,8 +4511,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,8 +4742,11 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4603,46 +4760,46 @@
         <v>100</v>
       </c>
       <c r="G66" s="3">
+        <v>100</v>
+      </c>
+      <c r="H66" s="3">
         <v>200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>100</v>
       </c>
       <c r="I66" s="3">
         <v>100</v>
       </c>
       <c r="J66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="K66" s="3">
         <v>700</v>
       </c>
       <c r="L66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="M66" s="3">
         <v>100</v>
       </c>
       <c r="N66" s="3">
+        <v>100</v>
+      </c>
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
-      </c>
-      <c r="P66" s="3">
-        <v>400</v>
       </c>
       <c r="Q66" s="3">
         <v>400</v>
       </c>
       <c r="R66" s="3">
+        <v>400</v>
+      </c>
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3">
-        <v>0</v>
-      </c>
       <c r="T66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U66" s="3">
         <v>100</v>
@@ -4650,8 +4807,8 @@
       <c r="V66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
+      <c r="W66" s="3">
+        <v>100</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
@@ -4662,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,70 +5156,73 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5060,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,71 +5464,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E76" s="3">
         <v>8800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,76 +5618,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5509,70 +5700,73 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E81" s="3">
         <v>-300</v>
       </c>
       <c r="F81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5583,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5808,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5673,8 +5871,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5685,8 +5883,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,70 +6268,73 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
         <v>-500</v>
       </c>
       <c r="F89" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
       </c>
       <c r="H89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-400</v>
       </c>
       <c r="K89" s="3">
         <v>-400</v>
       </c>
       <c r="L89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3">
         <v>-100</v>
       </c>
       <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6129,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,71 +6376,72 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
       </c>
       <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6231,8 +6451,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,71 +6605,74 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12500</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6453,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6519,8 +6752,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6555,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,17 +7019,20 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6815,20 +7060,20 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>13900</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -6851,8 +7096,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6901,8 +7149,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6910,8 +7158,8 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6925,71 +7173,74 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-700</v>
       </c>
       <c r="I102" s="3">
         <v>-700</v>
       </c>
       <c r="J102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6997,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
   <si>
     <t>AUST</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,8 +768,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -808,8 +812,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -844,8 +848,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -921,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,8 +1040,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,8 +1198,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1222,20 +1242,20 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1258,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1288,17 +1311,17 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>1000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>1200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1323,8 +1346,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,13 +1387,14 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E17" s="3">
         <v>300</v>
@@ -1376,7 +1403,7 @@
         <v>300</v>
       </c>
       <c r="G17" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H17" s="3">
         <v>500</v>
@@ -1388,46 +1415,46 @@
         <v>500</v>
       </c>
       <c r="K17" s="3">
+        <v>500</v>
+      </c>
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3">
         <v>100</v>
       </c>
       <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1438,13 +1465,16 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
@@ -1453,7 +1483,7 @@
         <v>-300</v>
       </c>
       <c r="G18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-500</v>
@@ -1465,46 +1495,46 @@
         <v>-500</v>
       </c>
       <c r="K18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
         <v>-100</v>
       </c>
       <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,34 +1577,35 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
@@ -1586,7 +1620,7 @@
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1595,23 +1629,23 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
       </c>
       <c r="W20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1655,11 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1630,64 +1667,64 @@
         <v>-600</v>
       </c>
       <c r="E21" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F21" s="3">
         <v>-300</v>
       </c>
       <c r="G21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-400</v>
       </c>
       <c r="N21" s="3">
         <v>-400</v>
       </c>
       <c r="O21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
+      <c r="X21" s="3">
+        <v>0</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
@@ -1698,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1739,8 +1779,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1775,8 +1815,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1784,64 +1827,64 @@
         <v>-600</v>
       </c>
       <c r="E23" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F23" s="3">
         <v>-300</v>
       </c>
       <c r="G23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1852,61 +1895,64 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,8 +2055,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2015,64 +2067,64 @@
         <v>-600</v>
       </c>
       <c r="E26" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F26" s="3">
         <v>-300</v>
       </c>
       <c r="G26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2083,8 +2135,11 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2092,64 +2147,64 @@
         <v>-600</v>
       </c>
       <c r="E27" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F27" s="3">
         <v>-300</v>
       </c>
       <c r="G27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,34 +2535,37 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
@@ -2510,7 +2580,7 @@
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2519,23 +2589,23 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
       </c>
       <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2615,11 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2554,64 +2627,64 @@
         <v>-600</v>
       </c>
       <c r="E33" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F33" s="3">
         <v>-300</v>
       </c>
       <c r="G33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,8 +2775,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2708,64 +2787,64 @@
         <v>-600</v>
       </c>
       <c r="E35" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F35" s="3">
         <v>-300</v>
       </c>
       <c r="G35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2776,79 +2855,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,73 +3002,74 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
-      </c>
-      <c r="E41" s="3">
-        <v>400</v>
       </c>
       <c r="F41" s="3">
         <v>400</v>
       </c>
       <c r="G41" s="3">
+        <v>400</v>
+      </c>
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3900</v>
-      </c>
-      <c r="P41" s="3">
-        <v>600</v>
       </c>
       <c r="Q41" s="3">
         <v>600</v>
       </c>
       <c r="R41" s="3">
+        <v>600</v>
+      </c>
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1200</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1600</v>
       </c>
       <c r="W41" s="3">
         <v>1600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
+      <c r="X41" s="3">
+        <v>1600</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
@@ -2993,64 +3080,67 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E42" s="3">
         <v>2600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
@@ -3061,8 +3151,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3070,8 +3160,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3135,8 +3228,8 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="X43" s="3">
+        <v>0</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
@@ -3147,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3188,8 +3284,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3224,8 +3320,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3265,18 +3364,18 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
@@ -3289,8 +3388,8 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
+      <c r="X45" s="3">
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
@@ -3301,73 +3400,76 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1300</v>
-      </c>
-      <c r="V46" s="3">
-        <v>1600</v>
       </c>
       <c r="W46" s="3">
         <v>1600</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
+      <c r="X46" s="3">
+        <v>1600</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
@@ -3378,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3426,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>100</v>
@@ -3435,17 +3540,17 @@
         <v>100</v>
       </c>
       <c r="U47" s="3">
+        <v>100</v>
+      </c>
+      <c r="V47" s="3">
         <v>200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>400</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,8 +3560,11 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3464,64 +3572,64 @@
         <v>5200</v>
       </c>
       <c r="E48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F48" s="3">
         <v>4800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>2300</v>
       </c>
       <c r="M48" s="3">
         <v>2300</v>
       </c>
       <c r="N48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1100</v>
-      </c>
-      <c r="V48" s="3">
-        <v>800</v>
       </c>
       <c r="W48" s="3">
         <v>800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="X48" s="3">
+        <v>800</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3532,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,8 +3880,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3807,11 +3927,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3828,8 +3948,8 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,74 +4040,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E54" s="3">
         <v>8400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1900</v>
-      </c>
-      <c r="U54" s="3">
-        <v>2600</v>
       </c>
       <c r="V54" s="3">
         <v>2600</v>
       </c>
       <c r="W54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X54" s="3">
         <v>2700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,8 +4182,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4070,46 +4201,46 @@
         <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
@@ -4117,8 +4248,8 @@
       <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+      <c r="X57" s="3">
+        <v>100</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -4129,8 +4260,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4206,8 +4340,11 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4250,15 +4387,15 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4274,8 +4411,8 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4283,13 +4420,16 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
@@ -4301,46 +4441,46 @@
         <v>100</v>
       </c>
       <c r="H60" s="3">
+        <v>100</v>
+      </c>
+      <c r="I60" s="3">
         <v>200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
       </c>
       <c r="J60" s="3">
         <v>100</v>
       </c>
       <c r="K60" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="L60" s="3">
         <v>700</v>
       </c>
       <c r="M60" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="N60" s="3">
         <v>100</v>
       </c>
       <c r="O60" s="3">
+        <v>100</v>
+      </c>
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>400</v>
       </c>
       <c r="R60" s="3">
         <v>400</v>
       </c>
       <c r="S60" s="3">
+        <v>400</v>
+      </c>
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
       <c r="U60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
@@ -4348,8 +4488,8 @@
       <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
+      <c r="X60" s="3">
+        <v>100</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
@@ -4360,8 +4500,11 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4437,8 +4580,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4478,8 +4624,8 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,13 +4900,16 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
@@ -4763,46 +4921,46 @@
         <v>100</v>
       </c>
       <c r="H66" s="3">
+        <v>100</v>
+      </c>
+      <c r="I66" s="3">
         <v>200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>100</v>
       </c>
       <c r="J66" s="3">
         <v>100</v>
       </c>
       <c r="K66" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="L66" s="3">
         <v>700</v>
       </c>
       <c r="M66" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="N66" s="3">
         <v>100</v>
       </c>
       <c r="O66" s="3">
+        <v>100</v>
+      </c>
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>400</v>
       </c>
       <c r="R66" s="3">
         <v>400</v>
       </c>
       <c r="S66" s="3">
+        <v>400</v>
+      </c>
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
       <c r="U66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V66" s="3">
         <v>100</v>
@@ -4810,8 +4968,8 @@
       <c r="W66" s="3">
         <v>100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
+      <c r="X66" s="3">
+        <v>100</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,73 +5330,76 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,74 +5650,77 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2700</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,79 +5810,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,8 +5895,11 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5712,64 +5907,64 @@
         <v>-600</v>
       </c>
       <c r="E81" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F81" s="3">
         <v>-300</v>
       </c>
       <c r="G81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5874,8 +6073,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,73 +6485,76 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-500</v>
       </c>
       <c r="F89" s="3">
         <v>-500</v>
       </c>
       <c r="G89" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
       </c>
       <c r="I89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-400</v>
       </c>
       <c r="L89" s="3">
         <v>-400</v>
       </c>
       <c r="M89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V89" s="3">
         <v>-100</v>
       </c>
       <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,74 +6597,75 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,74 +6835,77 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12500</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6755,8 +6989,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,20 +7265,23 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7063,20 +7309,20 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>13900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -7099,8 +7345,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7152,8 +7401,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -7161,8 +7410,8 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -7176,8 +7425,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7185,65 +7437,65 @@
         <v>200</v>
       </c>
       <c r="E102" s="3">
+        <v>200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-700</v>
       </c>
       <c r="J102" s="3">
         <v>-700</v>
       </c>
       <c r="K102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
